--- a/02_Zero_Shot/outputs/Embedding/MiniLM/RESULT_clap_minilm_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/MiniLM/RESULT_clap_minilm_zeroshot.xlsx
@@ -51489,7 +51489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2135390074149393</v>
+        <v>0.2135390074149394</v>
       </c>
     </row>
     <row r="4">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.631513845999507</v>
+        <v>25.73550172800242</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008771712819998356</v>
+        <v>0.008578500576000805</v>
       </c>
     </row>
   </sheetData>
